--- a/就職作品/原本_スケジュール.xlsx
+++ b/就職作品/原本_スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\就職作品\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\Employment\就職作品\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA00B09-FA5F-45D3-9E56-8DF89FD15604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9278E3-BBB0-467C-847C-67A610811B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="-13845" windowWidth="22965" windowHeight="12360" activeTab="2" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="2400" yWindow="-105" windowWidth="15915" windowHeight="15585" activeTab="4" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="5月" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
@@ -191,6 +191,16 @@
   <si>
     <t>採掘と納品</t>
   </si>
+  <si>
+    <t>採掘・納品</t>
+    <rPh sb="0" eb="2">
+      <t>サイクツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ノウヒン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -245,7 +255,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +295,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,7 +375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -436,6 +452,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2212,34 +2237,36 @@
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="D3" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
